--- a/frontend/public/templates/month_bill_import_template.xlsx
+++ b/frontend/public/templates/month_bill_import_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="month_bills" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="template" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>账期</t>
+          <t>账期(YYYYMM)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -434,45 +434,40 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>订购账号名称</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>订购账号名称</t>
+          <t>产品系列</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>产品系列</t>
+          <t>资源编号</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>资源编号</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>出账类型</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>出账类型</t>
+          <t>官网价格</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>官网价格</t>
+          <t>优惠价格</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>优惠价格</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>实付金额</t>
         </is>
